--- a/docs/slide_catalog.xlsx
+++ b/docs/slide_catalog.xlsx
@@ -10,11 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARS" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ICS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template Layouts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ARS'!$A$1:$I$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'TXN'!$A$1:$I$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ICS'!$A$1:$I$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Template Layouts'!$A$1:$F$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8713,4 +8715,479 @@
   <autoFilter ref="A1:I88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Layout Index</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Layout Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Key Placeholders</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Used For</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Cover / Intro - Slide 1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Title slide with logo area, 3 text sections, KPI images</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>ph[0] title, ph[32] subtitle, ph[14/33/34] 3 picture slots, ph[26-31] 3 paired header+body blocks, ph[19] body text</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Opening / title slide</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>3 picture placeholders for logos/icons; 3 header+body pairs for KPI text</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Cover / Intro - Slide 2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Minimal cover, centered title only</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>ph[0] title (6.3" x 0.9")</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Simple cover / closing</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>No content areas; title is center-positioned</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Divider - Slide 2</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Section divider with subtitle bar + large content area</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ph[0] title, ph[13] subtitle bar, ph[1] content (5.1" x 4.0")</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Section dividers between modules</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Left-aligned layout; content area can hold bullets or overview text</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Divider - Slide 3</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Minimal section divider with subtitle bar</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>ph[0] title, ph[13] subtitle bar</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Section dividers (minimal)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Full-width title; no content area beyond subtitle</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 1 (Chart + 2 Text)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Chart on left, 2 header+body text sections on right</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>ph[0] title, ph[13] subtitle, ph[14] picture (5.5" x 3.4" left), ph[26/19] top header+body, ph[27/28] bottom header+body</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>screenshot_kpi slides (chart + KPI callouts)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Right side has 2 independent text zones for insights/KPIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 2 (Chart + 1 Text)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Chart on left, single tall text section on right</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>ph[0] title, ph[13] subtitle, ph[14] picture (5.5" x 3.4" left), ph[26] header, ph[19] body (5.7" x 4.0" right)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>screenshot_kpi slides (chart + narrative)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Right body is 4" tall -- good for longer narratives or bullet lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 3 - Split</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Two equal content areas side-by-side</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ph[0] title, ph[13] subtitle, ph[14] left (5.8" x 4.3"), ph[1] right (5.8" x 4.3")</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>multi_screenshot (2 charts side-by-side)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Both zones are generic OBJECT placeholders; can hold images or text</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 4 - Split</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6-cell KPI grid (3 header+body pairs per column)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>ph[0] title, ph[13] subtitle, ph[26-30] left 3 pairs, ph[32-36] right 3 pairs</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>KPI summary / data grid slides</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>12 text placeholders total; designed for structured KPI readouts</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 5 - Thirds</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6-cell grid (3 columns x 2 rows of content blocks)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>ph[0] title, ph[13] subtitle, ph[1/15/16] top row, ph[17/19/20] bottom row</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Multi-chart grids, comparison panels</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Each cell is 3.6" x 2.1"; all OBJECT type (images or text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 6 - Main</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Full-width single content area (the workhorse screenshot layout)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>ph[0] title, ph[13] subtitle, ph[1] content (11.7" x 4.3")</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>screenshot (single full-width chart)</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Most common layout; used for any single chart/image</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 7 - Stacked Two</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2 rows: each has text on left + 3 pictures on right</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>ph[0] title, ph[15/35] row headers, ph[19/36] row body, ph[29-31] top 3 pics, ph[32-34] bottom 3 pics</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Before/after comparisons, multi-image galleries</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>6 picture placeholders (2.1" x 1.8" each); good for small chart grids</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 8 - Blank</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Blank slide with right-aligned title</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>ph[0] title (6.4" x 1.6", right side)</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Custom-built slides, freeform content</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>No content placeholders; shapes must be added programmatically</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 11 - Header1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Pure background / decorative header</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>(no placeholders)</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Visual separator, background-only</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>No usable placeholders; purely decorative</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 11 - Header2</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Background header with footer/slide number</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>ph[11] footer, ph[12] slide number</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Mailer summaries, wide charts (custom positioning)</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>No title/content placeholders; content placed via freeform shapes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/slide_catalog.xlsx
+++ b/docs/slide_catalog.xlsx
@@ -471,7 +471,7 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -560,7 +560,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Full-width bar; many categories</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -589,11 +593,11 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -601,7 +605,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Chart + product mix commentary</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -630,11 +638,11 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -642,7 +650,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Scatter + eligibility criteria explanation</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -671,11 +683,11 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -685,7 +697,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Stored in ctx.results</t>
+          <t>Trend line + rate narrative; stored in ctx.results</t>
         </is>
       </c>
     </row>
@@ -716,11 +728,11 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -728,7 +740,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Side-by-side comparison of two populations</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -757,11 +773,11 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_kpi</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -769,7 +785,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Chart + KPI callouts for current vs TTM</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -798,11 +818,11 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -810,7 +830,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Pair with DCTR-5 (Personal vs Business side-by-side)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -839,11 +863,11 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -851,7 +875,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Pair with DCTR-4 (Personal vs Business side-by-side)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -880,11 +908,11 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -892,7 +920,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Pair with DCTR-7 (L12M Personal vs Business)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -921,11 +953,11 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -933,7 +965,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Pair with DCTR-6 (L12M Personal vs Business)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -974,7 +1010,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; dense multi-group data</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1003,11 +1043,11 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1017,7 +1057,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Reads penetration results</t>
+          <t>Trend line + narrative on trajectory; reads penetration results</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1100,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; many segments x groups</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1103,7 +1147,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Merged pair</t>
+          <t>Merged pair (trajectory left, segments right)</t>
         </is>
       </c>
     </row>
@@ -1134,11 +1178,11 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1146,7 +1190,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Chart + segment insight callout</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1175,11 +1223,11 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1187,7 +1235,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Cohort curves + cohort explanation text</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1228,7 +1280,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Full-width detail breakdown</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1269,7 +1325,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Full-width heatmap; many branches x periods</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1302,7 +1362,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>wide_custom</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1312,7 +1372,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Wide layout</t>
+          <t>Wide layout; dense branch matrix</t>
         </is>
       </c>
     </row>
@@ -1343,11 +1403,11 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1355,7 +1415,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Bar + branch performance commentary</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1384,11 +1448,11 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>screenshot_kpi</t>
+          <t>kpi_grid</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1396,7 +1460,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>6-cell KPI grid for branch metrics</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1425,11 +1493,11 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1437,7 +1505,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Pair with DCTR-16 (rank left, change right)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1466,11 +1538,11 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1478,7 +1550,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Pair with DCTR-15 (rank left, change right)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1521,7 +1597,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Appendix</t>
+          <t>Appendix; full-width reference heatmap</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1642,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Merged pair</t>
+          <t>Merged pair (historical left, TTM right)</t>
         </is>
       </c>
     </row>
@@ -1597,11 +1673,11 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1609,7 +1685,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Funnel chart + stage-by-stage explanation</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1650,7 +1730,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Full-width detail bar</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1679,11 +1763,11 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1691,7 +1775,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Histogram + age distribution insights</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1720,11 +1808,11 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1732,7 +1820,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Donut + product mix narrative</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1761,11 +1853,11 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1773,7 +1865,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Natural comparison; split layout</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1802,11 +1898,11 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1814,7 +1910,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Chart + tier threshold explanation</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1843,11 +1943,11 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1855,7 +1955,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Scatter + correlation narrative</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1884,11 +1988,11 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1896,7 +2000,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Trend line + rate trajectory narrative</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1925,11 +2033,11 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1937,7 +2045,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Side-by-side comparison</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1966,11 +2078,11 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_kpi</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1978,7 +2090,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Chart + 2 KPI callout zones</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2007,11 +2123,11 @@
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>screenshot_kpi</t>
+          <t>kpi_grid</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2019,7 +2135,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>6-cell KPI grid for Reg E metrics</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2062,7 +2182,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Merged pair</t>
+          <t>Merged pair (opportunity left, detail right)</t>
         </is>
       </c>
     </row>
@@ -2093,11 +2213,11 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2105,7 +2225,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Chart + age-band commentary</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2146,7 +2270,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>Full-width heatmap; many tenure bands</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2220,11 +2348,11 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2232,7 +2360,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Funnel + stage explanation</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2265,7 +2397,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>wide_custom</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2275,7 +2407,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Wide layout</t>
+          <t>Wide layout; dense branch matrix</t>
         </is>
       </c>
     </row>
@@ -2306,11 +2438,11 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2318,7 +2450,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Bar + branch commentary</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2361,7 +2497,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Appendix</t>
+          <t>Appendix; full-width reference</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2540,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Full-width rank bar; many branches</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2433,11 +2573,11 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>screenshot_kpi</t>
+          <t>chart_kpi</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2445,7 +2585,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Chart + 2 KPI zones (rate + YoY change)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2474,11 +2618,11 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2486,7 +2630,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Hbar + duration distribution insights</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2529,7 +2677,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Merged pair</t>
+          <t>Merged pair (open left, closed right)</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2708,7 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -2572,7 +2720,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; many branches</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2601,11 +2753,11 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2613,7 +2765,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Chart + product attrition narrative</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2656,7 +2812,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Merged pair</t>
+          <t>Merged pair (personal left, business right)</t>
         </is>
       </c>
     </row>
@@ -2687,11 +2843,11 @@
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2699,7 +2855,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr"/>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Chart + tenure band insights</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2728,11 +2888,11 @@
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2740,7 +2900,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr"/>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>Chart + balance tier insights</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2769,11 +2933,11 @@
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>screenshot_kpi</t>
+          <t>chart_kpi</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2781,7 +2945,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Chart + retention rate + revenue KPIs</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2810,11 +2978,11 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>screenshot_kpi</t>
+          <t>chart_kpi</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2822,7 +2990,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr"/>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>Chart + mailer lift + response KPIs</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2851,11 +3023,11 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>screenshot_kpi</t>
+          <t>chart_kpi</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2863,7 +3035,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Chart + lost revenue + account count KPIs</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2896,7 +3072,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>screenshot_kpi</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2904,7 +3080,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr"/>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>Trend line + velocity narrative</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2933,11 +3113,11 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2945,7 +3125,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Natural comparison; ARS left vs Non-ARS right</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2974,11 +3158,11 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2986,7 +3170,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr"/>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>Waterfall + value buildup narrative</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3015,11 +3203,11 @@
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3027,7 +3215,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Waterfall + Reg E value narrative</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3056,11 +3248,11 @@
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>mailer_summary</t>
+          <t>kpi_grid</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3070,7 +3262,7 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>One per mailer month</t>
+          <t>6-cell KPI grid; one per mailer month</t>
         </is>
       </c>
     </row>
@@ -3101,11 +3293,11 @@
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3115,7 +3307,7 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Paired with monthly</t>
+          <t>Pair with Spend (swipes left, spend right)</t>
         </is>
       </c>
     </row>
@@ -3146,11 +3338,11 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3160,7 +3352,7 @@
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Paired with monthly</t>
+          <t>Pair with Swipes (swipes left, spend right)</t>
         </is>
       </c>
     </row>
@@ -3191,11 +3383,11 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3203,7 +3395,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>Trend line + response trajectory text</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3232,11 +3428,11 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3244,7 +3440,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>Trend line + rate commentary</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3273,11 +3473,11 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>mailer_summary</t>
+          <t>kpi_grid</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3285,7 +3485,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>Multi-KPI aggregate summary</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3314,11 +3518,11 @@
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3326,7 +3530,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>Chart + revisit pattern narrative</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3355,11 +3563,11 @@
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_kpi</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3367,7 +3575,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Chart + revenue lift + ROI KPIs</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3396,11 +3608,11 @@
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3408,7 +3620,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I70" s="3" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>Chart + driver analysis text</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3437,11 +3653,11 @@
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3449,7 +3665,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr"/>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Trend line + effectiveness narrative</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3478,11 +3698,11 @@
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>kpi_grid</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3490,7 +3710,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I72" s="3" t="inlineStr"/>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>6-cell KPI grid for ROI metrics</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3519,11 +3743,11 @@
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3531,7 +3755,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr"/>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>Chart + growth driver narrative</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3560,11 +3788,11 @@
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3572,7 +3800,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I74" s="3" t="inlineStr"/>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>Chart + risk factor narrative</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3601,11 +3833,11 @@
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3613,7 +3845,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>Chart + opportunity narrative</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3642,11 +3878,11 @@
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3654,7 +3890,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>Chart + program impact narrative</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3683,11 +3923,11 @@
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3695,7 +3935,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>Chart + actionable recommendations</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3724,11 +3968,11 @@
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>section_text</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3736,7 +3980,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr"/>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>Divider layout with conclusion text in content area</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3765,11 +4013,11 @@
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>section_text</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3777,7 +4025,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>Divider layout with conclusion text in content area</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3806,11 +4058,11 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>section_text</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -3818,7 +4070,11 @@
           <t>ODD</t>
         </is>
       </c>
-      <c r="I80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>Divider layout with conclusion text in content area</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I80"/>
@@ -3841,9 +4097,9 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3919,7 +4175,9 @@
           <t>Lollipop</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -3932,7 +4190,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Top 25</t>
+          <t>Full-width; top 25 merchants</t>
         </is>
       </c>
     </row>
@@ -3962,7 +4220,9 @@
           <t>Lollipop</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -3975,7 +4235,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Top 25</t>
+          <t>Full-width; top 25 merchants</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4265,9 @@
           <t>Lollipop</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -4018,7 +4280,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Top 25</t>
+          <t>Full-width; top 25 merchants</t>
         </is>
       </c>
     </row>
@@ -4049,13 +4311,21 @@
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>data_only</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Excel-only data table; no chart</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4084,13 +4354,21 @@
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>data_only</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Excel-only data table; no chart</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4119,13 +4397,21 @@
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>data_only</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Excel-only data table; no chart</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -4153,10 +4439,12 @@
           <t>3-Panel Bar</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>grid_thirds</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -4166,7 +4454,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Needs all 3 MCC results</t>
+          <t>3 panels in 3-col grid; needs all 3 MCC results</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4484,9 @@
           <t>Lollipop</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -4207,7 +4497,11 @@
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; many merchants</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4235,7 +4529,9 @@
           <t>Lollipop</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -4246,7 +4542,11 @@
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; many merchants</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4274,7 +4574,9 @@
           <t>Lollipop</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -4285,7 +4587,11 @@
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; many merchants</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -4313,7 +4619,9 @@
           <t>Lollipop</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -4326,7 +4634,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Caused #62 decompression bomb</t>
+          <t>Full-width; #62 decompression bomb fixed</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4664,9 @@
           <t>Lollipop</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -4367,7 +4677,11 @@
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; many merchants</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -4395,7 +4709,9 @@
           <t>Lollipop</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -4406,7 +4722,11 @@
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; many merchants</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -4434,10 +4754,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -4445,7 +4767,11 @@
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Trajectory line + rank movement commentary</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -4473,10 +4799,12 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_kpi</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -4484,7 +4812,11 @@
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Chart + top leader/decliner KPI callouts</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4512,8 +4844,14 @@
           <t>Scatter</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>chart_narrative</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
@@ -4521,7 +4859,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>No chart registered</t>
+          <t>Scatter + consistency explanation; no chart yet</t>
         </is>
       </c>
     </row>
@@ -4551,10 +4889,12 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -4562,7 +4902,11 @@
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Natural split: new left vs declining right</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4591,13 +4935,21 @@
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>data_only</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Excel-only table</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4626,13 +4978,21 @@
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>data_only</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Excel-only table</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4661,7 +5021,11 @@
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>data_only</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
@@ -4669,7 +5033,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Must run first; populates context</t>
+          <t>Engine step; populates context for downstream</t>
         </is>
       </c>
     </row>
@@ -4699,14 +5063,24 @@
           <t>KPI</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>kpi_grid</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>6-cell KPI grid: share, count, trend metrics</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4735,13 +5109,21 @@
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>data_only</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Excel-only table</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4769,7 +5151,9 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -4780,7 +5164,11 @@
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Full-width heatmap; many categories x competitors</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4808,14 +5196,24 @@
           <t>Table</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Split: business left vs personal right</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4843,14 +5241,24 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>chart_narrative</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Trend line + competitive shift narrative</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -4878,10 +5286,12 @@
           <t>Scatter</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -4889,7 +5299,11 @@
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Scatter + threat level explanation</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4917,10 +5331,12 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -4928,7 +5344,11 @@
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Chart + segmentation breakdown text</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -4957,7 +5377,11 @@
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>data_only</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
@@ -4965,7 +5389,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Data quality check</t>
+          <t>Data quality audit; Excel-only</t>
         </is>
       </c>
     </row>
@@ -4996,7 +5420,11 @@
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>data_only</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
@@ -5004,7 +5432,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Must run before M7B</t>
+          <t>Engine step; must run before M7B</t>
         </is>
       </c>
     </row>
@@ -5034,14 +5462,24 @@
           <t>KPI</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>kpi_grid</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>6-cell KPI grid for financial services metrics</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -5069,14 +5507,24 @@
           <t>KPI</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>kpi_grid</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>6-cell KPI grid for interchange metrics</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -5104,14 +5552,24 @@
           <t>KPI</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>kpi_grid</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>6-cell KPI grid for segment breakdown</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -5139,8 +5597,14 @@
           <t>Table/Charts</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>chart_narrative</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>TXN + ODD</t>
@@ -5148,7 +5612,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Requires ODD with generation col</t>
+          <t>Chart + demographic narrative; requires ODD generation col</t>
         </is>
       </c>
     </row>
@@ -5178,10 +5642,12 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -5189,7 +5655,11 @@
           <t>TXN CSV</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Chart + recurring merchant narrative</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -5217,10 +5687,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -5230,7 +5702,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Composite key</t>
+          <t>Trend line + onset timing narrative</t>
         </is>
       </c>
     </row>
@@ -5260,10 +5732,12 @@
           <t>Bullet Chart</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>grid_thirds</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -5273,7 +5747,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Must run last; reads all results</t>
+          <t>6-cell grid of bullet gauges; must run last</t>
         </is>
       </c>
     </row>
@@ -5298,9 +5772,9 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5376,14 +5850,24 @@
           <t>KPI Gauge</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>kpi_grid</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>6-cell KPI grid: total, open, closed, rate</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -5411,14 +5895,24 @@
           <t>KPI</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>kpi_grid</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Combine with ax01 on same KPI grid</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -5446,7 +5940,9 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -5457,7 +5953,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; many stat codes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -5485,10 +5985,12 @@
           <t>Donut</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -5496,7 +5998,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Donut + product mix commentary</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -5524,10 +6030,12 @@
           <t>Donut</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -5535,7 +6043,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Donut + debit penetration narrative</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -5563,7 +6075,9 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -5574,7 +6088,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; multi-group cross-tab</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -5602,7 +6120,9 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -5613,7 +6133,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Full-width heatmap; many branches</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -5641,10 +6165,12 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -5652,7 +6178,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Chart + penetration rate narrative</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -5680,10 +6210,12 @@
           <t>Donut</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -5693,7 +6225,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>REF/DM/Both</t>
+          <t>Donut + REF/DM/Both breakdown narrative</t>
         </is>
       </c>
     </row>
@@ -5723,7 +6255,9 @@
           <t>Stacked Bar</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -5734,7 +6268,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; complex stacked breakdown</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -5762,7 +6300,9 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -5773,7 +6313,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; multi-group cross-tab</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -5801,7 +6345,9 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -5812,7 +6358,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Full-width heatmap; many branches x sources</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -5840,10 +6390,12 @@
           <t>Donut</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -5853,7 +6405,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Biz vs Personal</t>
+          <t>Split: business left vs personal right</t>
         </is>
       </c>
     </row>
@@ -5883,10 +6435,12 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -5894,7 +6448,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Chart + year-over-year acquisition narrative</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -5922,10 +6480,12 @@
           <t>Waterfall</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -5933,7 +6493,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Waterfall + acquisition channel explanation</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -5962,13 +6526,21 @@
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>data_only</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Excel-only summary table</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -5996,7 +6568,9 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -6007,7 +6581,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Full-width heatmap; many branches</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -6035,10 +6613,12 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -6046,7 +6626,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Chart + DM debit activation narrative</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -6074,10 +6658,12 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -6085,7 +6671,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Chart + DM product mix narrative</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -6113,10 +6703,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -6124,7 +6716,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Trend line + DM acquisition trajectory</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -6152,14 +6748,24 @@
           <t>KPI</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>kpi_grid</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>6-cell KPI grid for DM activity metrics</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -6187,7 +6793,9 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -6198,7 +6806,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; many branches</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -6226,10 +6838,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -6237,7 +6851,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Trend line + monthly trajectory narrative</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -6266,13 +6884,21 @@
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>data_only</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Excel-only summary table</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -6300,7 +6926,9 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -6311,7 +6939,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Full-width heatmap; many branches</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -6339,10 +6971,12 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -6350,7 +6984,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Chart + REF debit activation narrative</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -6378,10 +7016,12 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -6389,7 +7029,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Chart + REF product mix narrative</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6417,10 +7061,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -6428,7 +7074,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Trend line + REF acquisition trajectory</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6456,14 +7106,24 @@
           <t>KPI</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>kpi_grid</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>6-cell KPI grid for REF activity metrics</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6491,7 +7151,9 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -6502,7 +7164,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; many branches</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6530,10 +7196,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -6541,7 +7209,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Trend line + monthly trajectory narrative</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6569,10 +7241,12 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -6580,7 +7254,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Split: ICS vs non-ICS age distributions</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6608,10 +7286,12 @@
           <t>Donut</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -6619,7 +7299,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Donut + closure pattern narrative</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6647,10 +7331,12 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -6658,7 +7344,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Natural split: open left vs closed right</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6686,10 +7376,12 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -6697,7 +7389,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Chart + balance tier distribution narrative</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -6725,7 +7421,9 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -6736,7 +7434,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Full-width heatmap; stat codes x open/close</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -6764,10 +7466,12 @@
           <t>Scatter</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -6775,7 +7479,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Scatter + age-balance correlation narrative</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -6803,7 +7511,9 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -6814,7 +7524,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; many tiers x breakdowns</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -6842,10 +7556,12 @@
           <t>Histogram</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -6853,7 +7569,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>Histogram + age distribution insights</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -6881,10 +7601,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -6892,7 +7614,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Trend line + balance trajectory narrative</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -6920,14 +7646,24 @@
           <t>KPI</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>kpi_grid</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>6-cell KPI grid: active, dormant, rates</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -6955,7 +7691,9 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -6966,7 +7704,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; multi-factor cross-tab</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -6994,10 +7736,12 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -7005,7 +7749,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Chart + balance-activity correlation narrative</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -7033,7 +7781,9 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -7044,7 +7794,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; many branches</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -7072,10 +7826,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -7083,7 +7839,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Trend line + monthly activity narrative</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -7111,10 +7871,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -7122,7 +7884,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Split: DM trend left vs REF trend right</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -7150,10 +7916,12 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -7161,7 +7929,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Chart + interchange revenue narrative</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -7189,10 +7961,12 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -7200,7 +7974,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Split: business left vs personal right</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -7228,7 +8006,9 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -7239,7 +8019,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Full-width heatmap; cohorts x months</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -7267,7 +8051,9 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -7278,7 +8064,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Full-width heatmap; cohorts x metrics</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -7306,10 +8096,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -7317,7 +8109,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr"/>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Milestone curves + activation timeline narrative</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -7345,10 +8141,12 @@
           <t>KPI</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>kpi_grid</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -7356,7 +8154,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr"/>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>6-cell KPI grid: activation rates by cohort</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -7384,10 +8186,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -7395,7 +8199,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr"/>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>Growth curves + pattern narrative</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -7423,10 +8231,12 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -7434,7 +8244,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Chart + persona profile narrative</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -7462,7 +8276,9 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -7473,7 +8289,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr"/>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; many branches</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -7501,10 +8321,12 @@
           <t>Funnel</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7512,7 +8334,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Funnel + stage-by-stage explanation</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -7540,10 +8366,12 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_kpi</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -7551,7 +8379,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr"/>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>Chart + revenue KPI callouts</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -7579,7 +8411,9 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -7590,7 +8424,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; many branches</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -7618,10 +8456,12 @@
           <t>Donut</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -7629,7 +8469,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr"/>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>Donut + source revenue narrative</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -7658,13 +8502,21 @@
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>data_only</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Action list; Excel-only table</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -7692,10 +8544,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -7703,7 +8557,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr"/>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>Decay curve + retention strategy narrative</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -7731,10 +8589,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -7742,7 +8602,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Growth line + portfolio health narrative</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -7770,10 +8634,12 @@
           <t>Scatter</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -7781,7 +8647,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Scatter + concentration risk narrative</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -7809,10 +8679,12 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -7820,7 +8692,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>Chart + source attrition narrative</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -7848,7 +8724,9 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -7859,7 +8737,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; many branches</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -7887,10 +8769,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -7898,7 +8782,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>Line + age-attrition correlation narrative</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -7926,10 +8814,12 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -7937,7 +8827,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>Chart + source growth narrative</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -7965,10 +8859,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -7976,7 +8872,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Trend line + closure rate narrative</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -8004,10 +8904,12 @@
           <t>Histogram</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8015,7 +8917,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I70" s="3" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>Histogram + activation speed narrative</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -8043,7 +8949,9 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -8054,7 +8962,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr"/>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; ranked branches</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -8082,7 +8994,9 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -8093,7 +9007,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I72" s="3" t="inlineStr"/>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; ranked products</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -8121,10 +9039,12 @@
           <t>Bubble</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -8132,7 +9052,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr"/>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>Bubble chart + persona definition narrative</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -8160,10 +9084,12 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -8171,7 +9097,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I74" s="3" t="inlineStr"/>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>Chart + contribution breakdown narrative</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -8199,7 +9129,9 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -8210,7 +9142,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>Full-width heatmap; personas x branches</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -8238,10 +9174,12 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -8249,7 +9187,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>Chart + source-persona narrative</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -8277,10 +9219,12 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -8288,7 +9232,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>Chart + per-persona revenue narrative</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -8317,13 +9265,21 @@
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>data_only</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr"/>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>Detail table; Excel-only</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -8351,10 +9307,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -8362,7 +9320,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>Velocity curves + spend trajectory narrative</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -8390,10 +9352,12 @@
           <t>Line</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8401,7 +9365,11 @@
           <t>ICS Excel</t>
         </is>
       </c>
-      <c r="I80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>Cohort lines + persona evolution narrative</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -8429,7 +9397,9 @@
           <t>Horizontal Bar</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -8440,7 +9410,11 @@
           <t>ICS + Referral</t>
         </is>
       </c>
-      <c r="I81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>Full-width; ranked referrer list</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -8468,10 +9442,12 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -8479,7 +9455,11 @@
           <t>ICS + Referral</t>
         </is>
       </c>
-      <c r="I82" s="3" t="inlineStr"/>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>Chart + emerging referrer narrative</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -8508,13 +9488,21 @@
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>data_only</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>ICS + Referral</t>
         </is>
       </c>
-      <c r="I83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>Action list; Excel-only</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -8542,10 +9530,12 @@
           <t>Donut</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -8553,7 +9543,11 @@
           <t>ICS + Referral</t>
         </is>
       </c>
-      <c r="I84" s="3" t="inlineStr"/>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>Split: one-time left vs repeat right</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -8581,10 +9575,12 @@
           <t>Grouped Bar</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -8592,7 +9588,11 @@
           <t>ICS + Referral</t>
         </is>
       </c>
-      <c r="I85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>Chart + staff impact narrative</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -8620,7 +9620,9 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -8631,7 +9633,11 @@
           <t>ICS + Referral</t>
         </is>
       </c>
-      <c r="I86" s="3" t="inlineStr"/>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>Full-width heatmap; branches x influence</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -8659,10 +9665,12 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>chart_narrative</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -8670,7 +9678,11 @@
           <t>ICS + Referral</t>
         </is>
       </c>
-      <c r="I87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>Chart + code health narrative</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -8698,8 +9710,14 @@
           <t>Multi-KPI</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>kpi_grid</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t>ICS + Referral</t>
@@ -8707,7 +9725,7 @@
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>Runs last; aggregates</t>
+          <t>6-cell KPI grid; runs last; aggregates</t>
         </is>
       </c>
     </row>

--- a/docs/slide_catalog.xlsx
+++ b/docs/slide_catalog.xlsx
@@ -10,13 +10,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARS" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ICS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template Layouts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slide Types" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template Layouts" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ARS'!$A$1:$I$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'TXN'!$A$1:$I$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ICS'!$A$1:$I$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Template Layouts'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Slide Types'!$A$1:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Template Layouts'!$A$1:$F$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9741,6 +9743,359 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Slide Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Layout Index</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Layout Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>When To Use</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Content Zones</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Examples</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>chart_narrative</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 2 (Chart + 1 Text)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Any chart that needs explanatory text -- trend lines, donuts, scatters, funnels, waterfalls</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Chart (5.5" x 3.4" left) + header + tall body (5.7" x 4.0" right)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>DCTR-1 trend, A7.8 funnel, A11.1 waterfall, ax08 source donut, ax29 milestones</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>chart_kpi</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 1 (Chart + 2 Text)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Charts with 2 KPI callout zones -- rates, snapshots, impact metrics with headline numbers</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Chart (5.5" x 3.4" left) + top header+body + bottom header+body (right)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>DCTR-3 snapshot, A8.3 Reg E snapshot, A9.1 attrition rate, A9.9-A9.11 impact KPIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 3 - Split</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Natural A-vs-B content -- Personal vs Business, Open vs Closed, DM vs REF, rank vs change</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Left content (5.8" x 4.3") + right content (5.8" x 4.3")</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>DCTR-4/5 personal vs business, A9.13 ARS vs non-ARS, ax14 age comparison, REF-4 one-time vs repeat</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>multi_screenshot</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 3 - Split</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Merged chart pairs -- two related charts that tell one story side by side</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Left content (5.8" x 4.3") + right content (5.8" x 4.3")</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>A7.6a trajectory+segments, A7.7 historical vs TTM, A8.5 opportunity, A9.3 open vs closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>kpi_grid</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 4 - Split</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Pure KPI summary slides -- structured readouts with 6 metric cells</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>6 cells: 3 header+body pairs per column (left 3, right 3)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>A7.10c branch KPIs, A8.12 Reg E summary, ax01/02 ICS summary, ax22 activity, REF-8 overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>grid_thirds</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 5 - Thirds</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Multi-panel charts -- 3+ small charts or comparison panels in a grid</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>6 cells: 3 columns x 2 rows (each 3.6" x 2.1")</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>MCC 3-panel comparison, portfolio scorecard bullet gauges</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 6 - Main</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Data-dense charts that need full width -- heatmaps, long merchant lists, many-branch bars</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Full-width content (11.7" x 4.3")</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>DCTR-8 summary, DCTR-9 heatmap, top-25 merchants, branch rank bars, cohort heatmaps</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>section_text</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Divider - Slide 2</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Text-only slides -- conclusions, section intros with explanatory content</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Title + subtitle bar + large text content area (5.1" x 4.0")</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>S6-S8 conclusions, section overview text</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>wide_custom</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Analysis - Slide 11 - Header2</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Dense matrices needing freeform positioning -- wide heatmaps, custom mailer layouts</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>No content placeholders; shapes added programmatically</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>A7.10a branch matrix, A8.4a branch Reg E matrix, mailer monthly summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>data_only</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>(no PPTX slide)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Excel-only tables and data engine steps -- no visual chart, no slide generated</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>N/A -- data appears in Excel report only</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>MCC tables, monthly movers, competitor detection, dormant lists, overview tables</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/docs/slide_catalog.xlsx
+++ b/docs/slide_catalog.xlsx
@@ -12,6 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ICS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slide Types" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template Layouts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Sources" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M Drive Paths" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="File Paths" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ARS'!$A$1:$I$80</definedName>
@@ -19,6 +22,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ICS'!$A$1:$I$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Slide Types'!$A$1:$F$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Template Layouts'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Data Sources'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'M Drive Paths'!$A$1:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'File Paths'!$A$1:$D$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10563,4 +10569,2783 @@
   <autoFilter ref="A1:F15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Source Location</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Key Columns</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ODD (raw)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>M:\CSM-Source\Folder\ClientID_ODDD*.xlsx</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Excel (.xlsx)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Account #, Date Opened, Date Closed, Stat Code, Prod Code, Branch, DOB, Balance fields</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Copied by retrieve_all() to retrieve_dir/CSM/YYYY.MM/ClientID/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ODD (formatted)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>watch_root\CSM\YYYY.MM\ClientID\*-formatted.xlsx</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Excel (.xlsx)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>All raw cols + Total Spend, Total Swipes, Avg Monthly, Account Age, Holder Age, Response Grouping, Segmentation</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Created by format_odd() 7-step pipeline; scan_ready_files() prefers these</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Client Config</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>M:\ARS\Config\clients_config.json  OR  config/clients_config.json</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>ClientID, DataStartDate, ICRate, NSF_OD_Fee, EligibleStatusCodes, BranchMapping</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Per-client overrides; falls back to defaults</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ARS Config</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>ars_config.json (project root or ARS_CONFIG_PATH env)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>paths (ars_base, watch_root, retrieve_dir), csm_sources, pipeline settings</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Loaded by ARSSettings; env vars with ARS_ prefix override</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Transaction CSV</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>User-provided or auto-discovered near ODD file</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>CSV/TXT (tab-delimited)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>merchant_name, amount, primary_account_num, transaction_date, mcc_code, business_flag, year_month</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>50+ column aliases auto-resolved by resolve_columns(); 13-col standard layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>ODD (for segments)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Via --odd CLI flag or Settings.odd_file</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Excel (.xlsx)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Account #, Segmentation cols (MmmYY Seg), ICS Account, generation, tenure, balance_tier</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Optional; enables M11 demographics, segment filters (ARS responders, ICS accounts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Transaction Dir</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Settings.transaction_dir (year-folder layout)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Directory of CSVs</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>YYYY/MM/*.csv files; auto-selects most recent 12 months</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Alternative to single file; V4 multi-month mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>ICS Excel</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>User-provided or M: drive</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Excel (.xlsx)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Account #, ICS Account (Yes/No), ICS Source (REF/DM/Both), Stat Code, Prod Code, Branch, Balance, Date Opened/Closed</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Core input; L12M monthly columns auto-discovered (MmmYY pattern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Referral Data</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Same ICS Excel or separate referral file</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Excel (.xlsx)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Referring Account, Referred Account, Referral Date, Referral Code, Branch</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Used by referral pipeline (REF-1 to REF-8); requires code_decoder for code classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Revenue Workbook</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>ICS directory or config path</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Excel (.xlsx)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Account #, Monthly Interchange, Annual Revenue</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Optional; enables revenue impact analyses (ax39, ax65, ax66)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Benchmarks</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>config/benchmarks.json</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>debit_penetration_rate, active_card_rate, avg_annual_spend_per_card, direct_mail_response_rate</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Industry benchmarks for comparison analyses</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>PPTX Template</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>packages/shared/src/shared/deck/template/Template12.25.pptx</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>PowerPoint (.pptx)</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>14 layouts (cover, divider, chart+text, split, grid, blank, etc.)</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Identical copies in ars_analysis and ics_toolkit packages</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Platform Config</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>config/platform.yaml</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>YAML</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>base_output_dir, m_drive_path, chart_theme, per-pipeline enabled/settings</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Top-level orchestrator config</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Read/Write</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Used By</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>M:\ARS\</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ARS base directory</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>All ARS operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>M:\ARS\Ready for Analysis\CSM\YYYY.MM\ClientID\</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Formatted ODD files (watch_root)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>scan, analyze, batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>M:\ARS\Incoming\ODDD Files\CSM\YYYY.MM\ClientID\</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Raw ODD files (retrieve_dir)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>retrieve_all()</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>M:\ARS\Presentations\Presentation Excels\</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Output Excel reports</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Write</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>excel_formatter, batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>M:\ARS\Presentations\Presentation Excels\Archive\</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Archived previous reports</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Write</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>batch (auto-archive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>M:\ARS\Presentations\Template12.25.pptx</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>PPTX template (runtime)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>deck_builder</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>M:\ARS\Scripts\Config\</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Runtime config directory</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ARSSettings</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>M:\ARS\Config\clients_config.json</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Master client config</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline context, per-client overrides</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>M:\ARS\Logs\</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline log files</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Write</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>All pipelines</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>M:\CSM-Source\{CSMName}\</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CSM source directories (per ars_config.json csm_sources)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>retrieve_all()</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>M:\ICS\Config\clients_config.json</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ICS client config fallback</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>ICS pipeline</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D91"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>File Path</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/config.py</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>PathsConfig, CSMSourcesConfig, PipelineConfig, ARSSettings (loads ars_config.json)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>shared/config.py</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>PlatformConfig (base_output_dir, m_drive_path, chart_theme, template_pptx, pipelines)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/settings.py</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Settings (data_file, odd_file, output_dir, charts, outputs, segments)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/settings.py</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>AppendSettings, AnalysisSettings, ReferralSettings</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>config/platform.yaml</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Top-level platform config (per-pipeline settings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>config/clients_config.json</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Master client config (DataStartDate, ICRate, NSF_OD_Fee, BranchMapping, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>config/benchmarks.json</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Industry benchmarks (debit penetration, active card rate, avg spend)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Data Loader</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>shared/data_loader.py</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>load_oddd(), load_tran(), load_odd(), _read_file() (auto-detect xlsx/xls/csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Data Loader</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/pipeline/steps/load.py</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Load ODD file for ARS pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Data Loader</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/data_loader.py</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>load_data(), load_odd(), merge_odd(), _apply_merchant_consolidation(), _derive_year_month()</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Data Loader</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/analysis/data_loader.py</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>load_data(), _normalize_strings(), _parse_dates(), _coerce_numerics(), discover L12M cols</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Data Loader</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/referral/data_loader.py</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Referral-specific data loading and normalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Retrieve/Format</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/pipeline/steps/retrieve.py</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>retrieve_all() -- copy ODD from CSM M: drive sources to retrieve_dir/CSM/YYYY.MM/ClientID/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Retrieve/Format</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>shared/format_odd.py</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>format_odd() 7-step pipeline (PYTD drop, totals, PIN+Sig, age, response, segmentation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Retrieve/Format</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/pipeline/steps/format.py</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>format_all() -- batch format from retrieve_dir to watch_root</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Retrieve/Format</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/pipeline/steps/scan.py</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>scan_ready_files(), _pick_best_file() (prefers *-formatted.xlsx), available_months/csms</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Column Mapping</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/column_map.py</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>COLUMN_ALIASES (50+ header variations), resolve_columns(), REQUIRED/OPTIONAL_COLUMNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Column Mapping</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/analysis/column_map.py</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>resolve_columns(), validate_columns(), discover_l12m_columns()</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Column Mapping</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/referral/column_map.py</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Referral column normalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Reference Data</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/competitor_patterns.py</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>COMPETITOR_MERCHANTS (7 categories, 3-tier matching), FINANCIAL_MCC_CODES, classify_merchant()</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Reference Data</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/segments.py</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>extract_responder_accounts(), extract_ics_accounts(), build_segment_filters()</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Reference Data</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/formatting.py</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>excel_number_format(), is_percentage_column(), is_grand_total_row()</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Reference Data</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/referral/code_decoder.py</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Referral code decoding and classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Reference Data</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/referral/scoring.py</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Referral scoring weights and calculations</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Deck Builder</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>shared/deck/__init__.py</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Re-exports: DeckBuilder, SlideContent, build_deck_from_results</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Deck Builder</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>shared/deck/engine.py</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>DeckBuilder class + SlideContent dataclass (extracted reusable engine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Deck Builder</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>shared/deck/universal.py</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>build_deck_from_results() -- universal builder for TXN/ICS/Attrition</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Deck Builder</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/output/deck_builder.py</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>ARS-specific deck builder (500+ lines, section ordering, mailer logic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Deck Builder</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/analysis/exports/deck_builder.py</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>ICS analysis deck builder</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Deck Builder</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/analysis/exports/pptx.py</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>ICS PPTX export helpers</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Deck Builder</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/analysis/exports/kpi_slides.py</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>ICS KPI slide builder</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Deck Builder</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/referral/exports/pptx.py</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>ICS referral deck builder</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Deck Builder</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/exports/pptx_report.py</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>TXN PPTX report (charts-only deck)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>shared/deck/template/Template12.25.pptx</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Shared PPTX template (14 layouts) -- canonical copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/output/template/Template12.25.pptx</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>ARS copy of template</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/templates/Template12.25.pptx</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>ICS copy of template</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Excel Export</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>shared/excel.py</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Shared Excel helpers (formatting, styles)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Excel Export</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/output/excel_formatter.py</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>ARS Excel report (Summary sheet, KPI extraction, per-section tabs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Excel Export</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/analysis/exports/excel.py</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>ICS analysis Excel report</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Excel Export</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/referral/exports/excel.py</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>ICS referral Excel report</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Excel Export</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/exports/excel_report.py</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>TXN Excel report (cover, TOC, per-analysis sheets, chart embeds)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>shared/charts.py</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Shared chart utilities (chart_figure context manager, style isolation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/charts/__init__.py</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>ARS chart registry + style</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/charts/guards.py</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>ARS matplotlib leak guards</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/charts/__init__.py</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>TXN chart registry (CHART_REGISTRY dict), create_charts(), render_chart_png()</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/charts/builders.py</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>TXN chart primitives (lollipop, donut, heatmap, grouped_bar, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/charts/theme.py</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>TXN chart theme + add_source_footer()</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/charts/{overall,personal,business,mcc,competitor,trends,recurring,scorecard}.py</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>TXN per-section chart functions</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/analysis/charts/__init__.py</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>ICS chart registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/analysis/charts/renderer.py</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>ICS chart renderer (PNG export)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/analysis/charts/{summary,source,dm_source,activity,demographics,cohort,performance,portfolio,persona,strategic}.py</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>ICS per-section chart functions</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/referral/charts/{top_referrers,branch_density,code_health,staff_multipliers,emerging_referrers}.py</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>ICS referral chart functions</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/analytics/registry.py</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>ARS module registry (ABC + @register)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/analytics/overview/{stat_codes,product_codes,eligibility}.py</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Overview: A1, A1b, A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/analytics/dctr/{penetration,trends,branches,funnel,overlays,_helpers}.py</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>DCTR: DCTR-1 to 16, A7.x (26 slides)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/analytics/rege/{status,branches,dimensions,_helpers}.py</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Reg E: A8.x (13 slides)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/analytics/attrition/{rates,dimensions,impact,_helpers}.py</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Attrition: A9.x (13 slides)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/analytics/value/analysis.py</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Value: A11.1, A11.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/analytics/mailer/{reach,response,impact,insights,cohort,_helpers}.py</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Mailer: A12-A15 (dynamic per month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/analytics/insights/{synthesis,conclusions,effectiveness,dormant,branch_scorecard,_data}.py</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Insights: S1-S8</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/analysis/analyses/{summary,source,dm_source,ref_source,demographics,activity,cohort,performance,portfolio,persona,strategic}.py</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>ICS: 82 chart slides across 12 sections</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/referral/analyses/{overview,top_referrers,branch_density,code_health,emerging_referrers,dormant_referrers,staff_multipliers,onetime_vs_repeat}.py</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Referral: REF-1 to REF-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/analyses/{overall,personal,business,mcc,financial_services,interchange,member_segments}.py</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>TXN: M1-M4, M7-M8, M10</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/analyses/{competitor_detect,competitor_metrics,competitor_segment,competitor_threat}.py</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>TXN: M6 competitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/analyses/{trends_rank,trends_growth,trends_consistency,trends_cohort,trends_movers}.py</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>TXN: M5 trends</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/analyses/{recurring,scorecard,spending_behavior,time_patterns}.py</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>TXN: M9, M15, behavioral</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>platform_app</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>platform_app/orchestrator.py</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Central orchestrator + _ensure_deck() fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/pipeline/runner.py</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>ARS pipeline runner (load -&gt; subset -&gt; analyze -&gt; generate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/pipeline/context.py</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>ARS PipelineContext dataclass</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/pipeline/batch.py</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>ARS batch runner (run_batch for 300+ clients)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>ars_analysis</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>ars_analysis/runner.py</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>ARS CLI entry point</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/analysis/pipeline.py</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>ICS analysis pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/referral/pipeline.py</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>ICS referral pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>ics_toolkit</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>ics_toolkit/runner.py</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>ICS CLI entry point</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/pipeline.py</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>TXN pipeline (load -&gt; analyze -&gt; chart -&gt; export)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>txn_analysis</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>txn_analysis/runner.py</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>TXN CLI entry point</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>platform_app</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>platform_app/pages/pipeline_ars.py</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Streamlit ARS pipeline page</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>platform_app</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>platform_app/pages/pipeline_txn.py</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Streamlit TXN pipeline page</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>platform_app</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>platform_app/pages/pipeline_ics.py</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Streamlit ICS pipeline page</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>platform_app</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>platform_app/pages/pipeline_attrition.py</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Streamlit Attrition pipeline page</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Script</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>run.bat</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>4-step pipeline: retrieve -&gt; format -&gt; batch -&gt; streamlit</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Script</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>run_batch.bat</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Headless batch runner</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Script</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>dashboard.bat</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Launch Streamlit UI only</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Script</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>setup.bat</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Environment setup (uv install)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>tests/e2e_data/1200_Test CU_2026.02.xlsx</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic ARS ODD (20 accounts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>tests/e2e_data/8888_transactions.csv</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic TXN (35 transactions)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>tests/e2e_data/9999_ICS_2026.01.xlsx</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic ICS (80 accounts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>tests/e2e_data/generate_fixtures.py</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>E2E fixture generator script</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>docs/slide_catalog.py</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>This file -- generates the catalog Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>docs/slide_catalog.xlsx</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Generated workbook (all tabs)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D91"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/slide_catalog.xlsx
+++ b/docs/slide_catalog.xlsx
@@ -15,6 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Sources" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M Drive Paths" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="File Paths" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Names" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross-Pipeline Fields" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ARS'!$A$1:$I$80</definedName>
@@ -25,6 +27,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Data Sources'!$A$1:$F$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'M Drive Paths'!$A$1:$D$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'File Paths'!$A$1:$D$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Field Names'!$A$1:$H$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cross-Pipeline Fields'!$A$1:$G$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4090,6 +4094,698 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ODD Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Used by ARS</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Used by TXN</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Used by ICS</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ARS Purpose</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TXN Purpose</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ICS Purpose</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Acct Number</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Yes (merge key)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Yes (merge key)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Joins TXN rows to ODD demographics</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Joins ICS append to ODD rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Stat Code</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Subset filtering, eligibility</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Account status filtering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Product Code / Prod Code</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility, product analysis</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Product-level ICS analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Date Opened</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Yes (merge)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>L12M filtering, age calc, attrition</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Account tenure</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Age calc, account age</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Date Closed</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Yes (merge)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Yes (optional)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Open/closed split, attrition</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Account status</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Open/closed filtering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Avg Bal</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Yes (merge)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Yes (optional)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Balance categorization</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Balance tier binning</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Balance analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Business?</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Yes (merge)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Personal/business split</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Business flag on TXN rows</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>P/B segmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Debit?</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Yes (merge)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>DCTR, Reg E, Value modules</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Debit flag on TXN rows</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Debit account filtering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Yes (merge)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Branch-level DCTR, attrition</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Branch on TXN rows</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Branch-level ICS analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Account Holder Age</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Yes (merge)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Demographics, age categories</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Generation cohort derivation</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>DOB</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Age computation in format_odd</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>MmmYY Spend</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Mailer impact, trends</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>L12M activity analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>MmmYY Swipes</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Mailer impact, trends</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>L12M activity analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>MmmYY Mail</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Mailer module, offer counting</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>MmmYY Resp</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Yes (segments)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Mailer module, segmentation</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Responder segment filters</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>MmmYY Reg E Code</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Reg E module analysis</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ICS Account</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Yes (segments)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>ICS segment filters</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Core analysis column</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ICS Source / Source</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>REF/DM/Both source analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Curr Bal</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Balance-tier analysis</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G20"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -13348,4 +14044,4097 @@
   <autoFilter ref="A1:D91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H102"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Aliases</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Acct Number</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Primary key for cross-pipeline merges</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Stat Code</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Status Code, StatCode, Stat_Code, Account Status</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Account status (O=Open, C=Closed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Product Code</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Prod Code, ProdCode, Prod_Code</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Product type identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Date Opened</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>DateOpened, Date_Opened, Open Date</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Account open date</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Date Closed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>DateClosed, Date_Closed, Close Date</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Account close date (NaT if open)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Avg Bal</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Balance, Current Balance, Cur Bal, AvgBal, Avg_Bal, Average Balance</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Average balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Branch identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Business?</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Business, BusinessFlag, Business Flag</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Personal vs business flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Debit?</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Debit, DC Indicator, DC_Indicator, DebitCard, Debit Card</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Debit card indicator (YES/Y/D/DC/DEBIT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>DOB</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Date of birth (used to compute age)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Mailable?</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility flag for mailers</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>MmmYY PIN $</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>e.g. Jan25 PIN $</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>PIN debit dollar amount per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>MmmYY Sig $</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>e.g. Jan25 Sig $</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Signature debit dollar amount per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>MmmYY PIN #</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>e.g. Jan25 PIN #</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>PIN debit transaction count per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>MmmYY Sig #</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>e.g. Jan25 Sig #</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Signature debit transaction count per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>MmmYY MTD</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>e.g. Jan25 MTD</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Month-to-date items</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>MmmYY OD Limit</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>e.g. Jan25 OD Limit</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Overdraft limit per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>MmmYY Reg E Code</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>e.g. Jan25 Reg E Code</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Reg E status code per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>MmmYY Reg E Desc</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>e.g. Jan25 Reg E Desc</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Reg E description per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>MmmYY Mail</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>e.g. Jan25 Mail</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Mailer segment code per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>MmmYY Resp</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>e.g. Jan25 Resp</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Raw Excel</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Response segment code per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>MmmYY Spend</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>e.g. Jan25 Spend</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>PIN $ + Sig $ combined per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>MmmYY Swipes</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>e.g. Jan25 Swipes</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>PIN # + Sig # combined per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Total Spend</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Sum of all monthly Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Total Swipes</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Sum of all monthly Swipes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Total Items</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Sum of all monthly MTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>last 3-mon spend</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Last 3 months cumulative spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>last 3-mon swipes</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Last 3 months cumulative swipes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Last 3-mon Items</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Last 3 months cumulative items</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>last 12-mon spend</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Last 12 months cumulative spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>last 12-mon swipes</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Last 12 months cumulative swipes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Last 12-mon Items</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Last 12 months cumulative items</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>MonthlySpend12</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>12-month avg monthly spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>MonthlySwipes12</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>12-month avg monthly swipes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>MonthlyItems12</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>12-month avg monthly items</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>MonthlySpend3</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>3-month avg monthly spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>MonthlySwipes3</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>3-month avg monthly swipes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>MonthlyItems3</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>3-month avg monthly items</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>SwipeCat12</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>12-month swipe tier (Non-user, 1-5, 6-10, 11-20, 21-40, 41+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>SwipeCat3</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>3-month swipe tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Account Holder Age</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Years from DOB to report date</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Account Age</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Years from Date Opened to close/report date</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t># of Offers</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Count of non-null Mail columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t># of Responses</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Count of non-null Resp columns (excl NU 1-4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Response Grouping</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>No Offer / Non-Responder / SO-SR / MO-SR / MR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>MmmYY Segmentation</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>e.g. Jan25 Segmentation</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>format_odd</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Control / Non-Responder / Responder per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>ICS Account</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>ICS append</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Yes / No (appended by ICS pipeline)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>ICS Source</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>ICS append</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>REF / DM / Both / empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>merchant_name</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>merchantname, merchant, merch_name, description, payee, vendor, ...</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Merchant/payee name (12 aliases)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>transaction_amount, txn_amount, amt, debit_amount, purchase_amount, ...</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Transaction dollar amount (11 aliases)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>primary_account_num</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>account_number, acct_num, card_number, pan, member_number, ...</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Account identifier (18 aliases)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>transaction_date</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>trans_date, txn_date, date, posting_date, settlement_date, ...</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Transaction date (12 aliases)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>mcc_code</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>mcccode, mcc, merchant_category_code, sic_code, sic</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Merchant Category Code (7 aliases)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>business_flag</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>businessflag, business, is_business, account_type</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Business account indicator (6 aliases)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>year_month</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>yearmonth, ym</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Pre-computed YYYY-MM period</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>V4 Positional</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>transaction_type</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Tab file col 3</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Transaction type code</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>V4 Positional</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>terminal_location_1</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr"/>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Tab file col 7</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Terminal location line 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>V4 Positional</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>terminal_location_2</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Tab file col 8</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Terminal location line 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>V4 Positional</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>terminal_id</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr"/>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Tab file col 9</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Terminal identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>V4 Positional</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>merchant_id</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Tab file col 10</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Merchant identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>V4 Positional</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>institution</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr"/>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Tab file col 11</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Issuing institution</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>V4 Positional</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>card_present</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Tab file col 12</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Card-present indicator</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>V4 Positional</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>transaction_code</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Tab file col 13</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Transaction code</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>merchant_consolidated</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>data_loader</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Standardized merchant name via rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>year_month</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>(if not in CSV)</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>data_loader</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>YYYY-MM derived from transaction_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>is_partial_month</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>data_loader</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>True if last month has &lt;90% day coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>data_loader</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Originating CSV filename</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>generation</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>ODD merge</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Gen Z / Millennial / Gen X / Boomer / Silent</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>balance_tier</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>ODD merge</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Low / Medium / High / Very High</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>tenure_years</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>ODD merge</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Years since account opened</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>ICS Account</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>ICS Accounts, Ics Account, ICS_Account, IcsAccount</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>ICS account flag (Yes/No)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Stat Code</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>StatCode, Stat_Code, Status Code</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>Account status code</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Debit?</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Debit, DebitCard, Debit Card</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Debit card indicator</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Business?</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Business, BusinessFlag, Business Flag</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>Personal vs business flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Date Opened</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>DateOpened, Date_Opened, Open Date</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Account open date</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Prod Code</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>ProdCode, Prod_Code, Product Code</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>Product code</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr"/>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>Branch identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr"/>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>ICS source (REF/DM/Both)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Curr Bal</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>CurrBal, Curr_Bal, Current Balance</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>Current balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Date Closed</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>DateClosed, Date_Closed, Close Date</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>Account close date</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Avg Bal</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>AvgBal, Avg_Bal, Average Balance, AvgColBal</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>Average balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>L12M</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>MmmYY Swipes</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>regex: ^[A-Z][a-z]{2}\d{2} Swipes$</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>Monthly swipe count (e.g. Feb24 Swipes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>L12M</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>MmmYY Spend</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>regex: ^[A-Z][a-z]{2}\d{2} Spend$</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>Monthly spend (e.g. Feb24 Spend)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Total L12M Swipes</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr"/>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>utils.py</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>Sum of all MmmYY Swipes columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Total L12M Spend</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr"/>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>utils.py</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>Sum of all MmmYY Spend columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Active in L12M</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr"/>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>utils.py</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>True if Total L12M Swipes &gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Opening Month</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr"/>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>utils.py</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>YYYY-MM from Date Opened</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Account Age Days</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr"/>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>utils.py</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>Days since Date Opened</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Balance Tier</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr"/>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>utils.py</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>Binned from Curr Bal</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>ICS</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Age Range</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr"/>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>utils.py</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>Binned from Account Age Days</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>ICS Append</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>ICS Account</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr"/>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>matcher.py</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>Yes / No (appended to ODD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>ICS Append</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>ICS Source</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr"/>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>matcher.py</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>REF / DM / Both / empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>ICS Append</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Acct Hash</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr"/>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>merger.py</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>Normalized account hash from REF/DM files</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>ICS Referral</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Referrer Name</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>referrer, referrer_name</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>Person who made the referral</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>ICS Referral</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Issue Date</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>issue_date, date</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>Referral issue date</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>ICS Referral</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Referral Code</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>referral_code, code</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>Referral code identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>ICS Referral</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Purchase Manager</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>purchase_manager, staff</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>Staff member / purchase manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>ICS Referral</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>branch_id</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>Branch identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>ICS Referral</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>account_holder, new_account</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>New account holder name</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>ICS Referral</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>MRDB Account Hash</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>mrdb_account_hash, mrdb, account_hash</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>Account hash for matching</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>ICS Referral</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Cert ID</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>cert_id, certificate_id</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>Certificate identifier</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H102"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>